--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N151_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N151_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.36322415264289</v>
+        <v>3.14652392480447</v>
       </c>
       <c r="D2" t="n">
-        <v>17.64680482383459</v>
+        <v>2.867605783873121</v>
       </c>
       <c r="E2" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F2" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.61463081108128</v>
+        <v>12.77487750680071</v>
       </c>
       <c r="D3" t="n">
-        <v>80.37837640783893</v>
+        <v>13.06148616627383</v>
       </c>
       <c r="E3" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F3" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.09611249425851</v>
+        <v>7.490618280317007</v>
       </c>
       <c r="D4" t="n">
-        <v>47.92312324505959</v>
+        <v>7.787507527322184</v>
       </c>
       <c r="E4" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F4" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.04040338571947</v>
+        <v>4.881565550179414</v>
       </c>
       <c r="D5" t="n">
-        <v>28.44268561264062</v>
+        <v>4.6219364120541</v>
       </c>
       <c r="E5" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F5" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.83459407863647</v>
+        <v>2.410621537778426</v>
       </c>
       <c r="D6" t="n">
-        <v>16.65404735676677</v>
+        <v>2.7062826954746</v>
       </c>
       <c r="E6" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F6" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.23305069597201</v>
+        <v>7.025370738095452</v>
       </c>
       <c r="D7" t="n">
-        <v>45.11209717288842</v>
+        <v>7.330715790594368</v>
       </c>
       <c r="E7" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F7" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1.23353351728746</v>
+        <v>0.2004491965592123</v>
       </c>
       <c r="D8" t="n">
-        <v>28.31204837917327</v>
+        <v>4.600707861615657</v>
       </c>
       <c r="E8" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F8" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0338370744882</v>
+        <v>2.767998524604333</v>
       </c>
       <c r="D9" t="n">
-        <v>17.37840845351762</v>
+        <v>2.823991373696614</v>
       </c>
       <c r="E9" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F9" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.00541663286132</v>
+        <v>8.125880202839964</v>
       </c>
       <c r="D10" t="n">
-        <v>49.73181517749741</v>
+        <v>8.081419966343329</v>
       </c>
       <c r="E10" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F10" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.262499595037452</v>
+        <v>1.342656184193586</v>
       </c>
       <c r="D11" t="n">
-        <v>8.126282722686613</v>
+        <v>1.320520942436575</v>
       </c>
       <c r="E11" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F11" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.1313518427005</v>
+        <v>5.058844674438832</v>
       </c>
       <c r="D12" t="n">
-        <v>31.18061144505624</v>
+        <v>5.06684935982164</v>
       </c>
       <c r="E12" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F12" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.45079743659623</v>
+        <v>5.435754583446888</v>
       </c>
       <c r="D13" t="n">
-        <v>33.5862659565646</v>
+        <v>5.457768217941748</v>
       </c>
       <c r="E13" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F13" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.57906166147556</v>
+        <v>6.106597519989779</v>
       </c>
       <c r="D14" t="n">
-        <v>34.87292628464553</v>
+        <v>5.666850521254899</v>
       </c>
       <c r="E14" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F14" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.48339374388746</v>
+        <v>5.116051483381713</v>
       </c>
       <c r="D15" t="n">
-        <v>39.08298602135459</v>
+        <v>6.350985228470122</v>
       </c>
       <c r="E15" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F15" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>20.91451254932821</v>
+        <v>3.398608289265834</v>
       </c>
       <c r="D16" t="n">
-        <v>21.10456905973603</v>
+        <v>3.429492472207106</v>
       </c>
       <c r="E16" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F16" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>11.73325107866501</v>
+        <v>1.906653300283063</v>
       </c>
       <c r="D17" t="n">
-        <v>8.992211993898382</v>
+        <v>1.461234449008487</v>
       </c>
       <c r="E17" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F17" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.8806130178211</v>
+        <v>3.393099615395929</v>
       </c>
       <c r="D18" t="n">
-        <v>30.3848516336076</v>
+        <v>4.937538390461235</v>
       </c>
       <c r="E18" t="n">
-        <v>18.10034569226478</v>
+        <v>2.941306174993028</v>
       </c>
       <c r="F18" t="n">
-        <v>17.22282054149679</v>
+        <v>2.798708337993228</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
